--- a/data/trans_orig/IP13_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP13_2023-Clase-trans_orig.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables originales" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2023" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q25"/>
+  <dimension ref="A1:W32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -524,12 +524,18 @@
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si se han tenido que quedar más de la mitad del día en la cama por dolor o síntomas en 2023 (Tasa respuesta: 99,9%)</t>
+          <t>Menores según si se han tenido que quedar más de la mitad del día en la cama por dolor o síntomas 2023 en 2023 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -542,24 +548,30 @@
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="n"/>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>Niño</t>
         </is>
       </c>
-      <c r="I1" s="3" t="n"/>
-      <c r="J1" s="3" t="n"/>
       <c r="K1" s="3" t="n"/>
       <c r="L1" s="3" t="n"/>
-      <c r="M1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
+      <c r="M1" s="3" t="n"/>
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="n"/>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="n"/>
+      <c r="S1" s="3" t="n"/>
+      <c r="T1" s="3" t="n"/>
+      <c r="U1" s="3" t="n"/>
+      <c r="V1" s="3" t="n"/>
+      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -576,65 +588,95 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
+          <t>N (lím inf IC)</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>N (lím sup IC)</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
           <t>Estimación puntual</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>lím inf IC</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>n (muestra)</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>N (estimada)</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>N (lím inf IC)</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>N (lím sup IC)</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>Estimación puntual</t>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="O2" s="3" t="inlineStr">
         <is>
           <t>lím inf IC</t>
         </is>
       </c>
-      <c r="L2" s="3" t="inlineStr">
+      <c r="P2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
       </c>
-      <c r="M2" s="3" t="inlineStr">
+      <c r="Q2" s="3" t="inlineStr">
         <is>
           <t>n (muestra)</t>
         </is>
       </c>
-      <c r="N2" s="3" t="inlineStr">
+      <c r="R2" s="3" t="inlineStr">
         <is>
           <t>N (estimada)</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
+      <c r="S2" s="3" t="inlineStr">
+        <is>
+          <t>N (lím inf IC)</t>
+        </is>
+      </c>
+      <c r="T2" s="3" t="inlineStr">
+        <is>
+          <t>N (lím sup IC)</t>
+        </is>
+      </c>
+      <c r="U2" s="3" t="inlineStr">
         <is>
           <t>Estimación puntual</t>
         </is>
       </c>
-      <c r="P2" s="3" t="inlineStr">
+      <c r="V2" s="3" t="inlineStr">
         <is>
           <t>lím inf IC</t>
         </is>
       </c>
-      <c r="Q2" s="3" t="inlineStr">
+      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -658,6 +700,12 @@
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
       <c r="Q3" s="2" t="n"/>
+      <c r="R3" s="2" t="n"/>
+      <c r="S3" s="2" t="n"/>
+      <c r="T3" s="2" t="n"/>
+      <c r="U3" s="2" t="n"/>
+      <c r="V3" s="2" t="n"/>
+      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -667,70 +715,112 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>6639</v>
+          <t>Sí, por algún síntoma</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2866</t>
+        </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>1070</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>6700</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>5038</v>
+          <t>2,74%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>6,41%</t>
+        </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>3331</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="N4" s="2" t="n">
-        <v>11677</v>
+          <t>915</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>7818</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>2,45%</t>
+        </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>6197</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>2780</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>11587</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>2,58%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>1,16%</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
+          <t>4,82%</t>
         </is>
       </c>
     </row>
@@ -738,70 +828,112 @@
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>147</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>97823</v>
+          <t>Sí, por algún dolor</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3773</t>
+        </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>1323</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>8022</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>164</v>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>131146</v>
+          <t>3,61%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>7,68%</t>
+        </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>1707</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="n">
-        <v>311</v>
-      </c>
-      <c r="N5" s="2" t="n">
-        <v>228969</v>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>6129</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>1,25%</t>
+        </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>5479</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>2283</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>11530</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>2,28%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>0,95%</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -809,216 +941,342 @@
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>157</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>104462</v>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>97823</t>
+        </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>93172</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>101241</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>170</v>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>136184</v>
+          <t>93,65%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>89,19%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>96,92%</t>
+        </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>164</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>131146</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="n">
-        <v>327</v>
-      </c>
-      <c r="N6" s="2" t="n">
-        <v>240646</v>
+          <t>125432</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>134255</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>96,3%</t>
+        </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>311</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>228969</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>222118</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>234503</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>95,15%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>92,3%</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>97,45%</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>Grupo III</t>
-        </is>
-      </c>
+      <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>5015</v>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>104462</t>
+        </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>104462</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>104462</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="I7" s="2" t="n">
-        <v>8885</v>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>170</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>136184</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="N7" s="2" t="n">
-        <v>13900</v>
+          <t>136184</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>136184</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>327</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>240646</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>240646</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>240646</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n"/>
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>134</v>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>89666</v>
+          <t>Sí, por algún síntoma</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4364</t>
+        </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>1511</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>8438</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>118</v>
-      </c>
-      <c r="I8" s="2" t="n">
-        <v>86688</v>
+          <t>4,61%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1,6%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>8,91%</t>
+        </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>6356</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="n">
-        <v>252</v>
-      </c>
-      <c r="N8" s="2" t="n">
-        <v>176354</v>
+          <t>3247</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>11938</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>6,65%</t>
+        </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>10719</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>6382</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>16584</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>5,63%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>3,35%</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>8,72%</t>
         </is>
       </c>
     </row>
@@ -1026,145 +1284,225 @@
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>141</v>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>94681</v>
+          <t>Sí, por algún dolor</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>651</t>
+        </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>3809</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>131</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>95573</v>
+          <t>0,69%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>4,02%</t>
+        </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>2529</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="n">
-        <v>272</v>
-      </c>
-      <c r="N9" s="2" t="n">
-        <v>190254</v>
+          <t>548</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>7031</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>2,65%</t>
+        </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>3181</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>968</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>7498</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Grupo IV y V</t>
-        </is>
-      </c>
+      <c r="A10" s="1" t="n"/>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>2747</v>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>89666</t>
+        </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>84932</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>92532</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>3453</v>
+          <t>94,7%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>89,7%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>97,73%</t>
+        </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>118</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>86688</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>6200</v>
+          <t>80612</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>90482</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>90,7%</t>
+        </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>176354</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>168994</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>181393</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>92,69%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>88,83%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>95,34%</t>
         </is>
       </c>
     </row>
@@ -1172,216 +1510,342 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>49114</v>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>94681</t>
+        </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94681</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>94681</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>79</v>
-      </c>
-      <c r="I11" s="2" t="n">
-        <v>60400</v>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>131</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>95573</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="n">
-        <v>149</v>
-      </c>
-      <c r="N11" s="2" t="n">
-        <v>109514</v>
+          <t>95573</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>95573</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>190254</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>190254</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>190254</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n"/>
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>75</v>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>51861</v>
+          <t>Sí, por algún síntoma</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1687</t>
+        </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>395</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>4947</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>84</v>
-      </c>
-      <c r="I12" s="2" t="n">
-        <v>63853</v>
+          <t>3,25%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>9,54%</t>
+        </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>2904</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="n">
-        <v>159</v>
-      </c>
-      <c r="N12" s="2" t="n">
-        <v>115714</v>
+          <t>859</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>7336</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>4,55%</t>
+        </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>4591</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>9385</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>3,97%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>1,73%</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>8,11%</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>Grupo VI</t>
-        </is>
-      </c>
+      <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>8901</v>
+          <t>Sí, por algún dolor</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1060</t>
+        </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>3970</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="I13" s="2" t="n">
-        <v>15897</v>
+          <t>2,04%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>7,66%</t>
+        </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>549</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="N13" s="2" t="n">
-        <v>24798</v>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>2931</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,86%</t>
+        </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1609</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>389</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>4643</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -1392,67 +1856,109 @@
           <t>No</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n">
-        <v>264</v>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>209109</v>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>49114</t>
+        </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>45277</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>50816</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>263</v>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>202375</v>
+          <t>94,7%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>87,31%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>97,98%</t>
+        </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>79</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>60400</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="n">
-        <v>527</v>
-      </c>
-      <c r="N14" s="2" t="n">
-        <v>411484</v>
+          <t>55635</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>62553</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>94,59%</t>
+        </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>87,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>109514</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>104494</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>112453</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>94,64%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>90,3%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>97,18%</t>
         </is>
       </c>
     </row>
@@ -1463,20 +1969,24 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="C15" s="2" t="n">
-        <v>277</v>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>218010</v>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>51861</t>
+        </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>51861</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>51861</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1484,32 +1994,40 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="H15" s="2" t="n">
-        <v>285</v>
-      </c>
-      <c r="I15" s="2" t="n">
-        <v>218272</v>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>84</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>63853</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="n">
-        <v>562</v>
-      </c>
-      <c r="N15" s="2" t="n">
-        <v>436282</v>
+          <t>63853</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>63853</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1522,6 +2040,36 @@
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>115714</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>115714</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>115714</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1530,75 +2078,117 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Grupo VII</t>
+          <t>Grupo VI</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>10391</v>
+          <t>Sí, por algún síntoma</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>6148</t>
+        </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>2748</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>11271</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="I16" s="2" t="n">
-        <v>9914</v>
+          <t>2,82%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,26%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>5,17%</t>
+        </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>11528</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="N16" s="2" t="n">
-        <v>20305</v>
+          <t>6489</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>18479</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>5,28%</t>
+        </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>17676</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>11042</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>26218</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>4,05%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>2,53%</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>6,01%</t>
         </is>
       </c>
     </row>
@@ -1606,70 +2196,112 @@
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="n">
-        <v>163</v>
-      </c>
-      <c r="D17" s="2" t="n">
-        <v>109037</v>
+          <t>Sí, por algún dolor</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2753</t>
+        </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>702</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>7525</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="n">
-        <v>184</v>
-      </c>
-      <c r="I17" s="2" t="n">
-        <v>152703</v>
+          <t>1,26%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>3,45%</t>
+        </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>4369</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="n">
-        <v>347</v>
-      </c>
-      <c r="N17" s="2" t="n">
-        <v>261740</v>
+          <t>1716</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>9366</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>2,0%</t>
+        </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>7122</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>3439</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>13305</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>1,63%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -1677,216 +2309,342 @@
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="n">
-        <v>180</v>
-      </c>
-      <c r="D18" s="2" t="n">
-        <v>119428</v>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>209109</t>
+        </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>202395</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>213329</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="n">
-        <v>198</v>
-      </c>
-      <c r="I18" s="2" t="n">
-        <v>162617</v>
+          <t>95,92%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>92,84%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>97,85%</t>
+        </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>263</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>202375</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="n">
-        <v>378</v>
-      </c>
-      <c r="N18" s="2" t="n">
-        <v>282045</v>
+          <t>194944</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>208535</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>92,72%</t>
+        </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>527</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>411484</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>401347</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>419328</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>94,32%</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>91,99%</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>96,11%</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>No ha trabajado</t>
-        </is>
-      </c>
+      <c r="A19" s="1" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="D19" s="2" t="n">
-        <v>3744</v>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>218010</t>
+        </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>218010</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>218010</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="I19" s="2" t="n">
-        <v>3421</v>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>285</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>218272</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="N19" s="2" t="n">
-        <v>7165</v>
+          <t>218272</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>218272</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>562</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>436282</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>436282</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>436282</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n"/>
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="n">
-        <v>93</v>
-      </c>
-      <c r="D20" s="2" t="n">
-        <v>65151</v>
+          <t>Sí, por algún síntoma</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>8865</t>
+        </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>4910</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>14283</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="n">
-        <v>86</v>
-      </c>
-      <c r="I20" s="2" t="n">
-        <v>68582</v>
+          <t>7,42%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>4,11%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>11,96%</t>
+        </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="n">
-        <v>179</v>
-      </c>
-      <c r="N20" s="2" t="n">
-        <v>133733</v>
+          <t>3750</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>13902</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>4,43%</t>
+        </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>16069</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>9924</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>23818</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>5,7%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>3,52%</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>8,44%</t>
         </is>
       </c>
     </row>
@@ -1894,145 +2652,225 @@
       <c r="A21" s="1" t="n"/>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="n">
-        <v>99</v>
-      </c>
-      <c r="D21" s="2" t="n">
-        <v>68895</v>
+          <t>Sí, por algún dolor</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>1527</t>
+        </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>388</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>4265</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>90</v>
-      </c>
-      <c r="I21" s="2" t="n">
-        <v>72003</v>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>3,57%</t>
+        </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>2710</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="n">
-        <v>189</v>
-      </c>
-      <c r="N21" s="2" t="n">
-        <v>140898</v>
+          <t>530</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>7066</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>1,67%</t>
+        </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>4236</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>1827</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>9037</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>1,5%</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
+      <c r="A22" s="1" t="n"/>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="n">
-        <v>58</v>
-      </c>
-      <c r="D22" s="2" t="n">
-        <v>37437</v>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>109037</t>
+        </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>103695</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>113497</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="n">
-        <v>64</v>
-      </c>
-      <c r="I22" s="2" t="n">
-        <v>46608</v>
+          <t>91,3%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>86,83%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>95,03%</t>
+        </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>184</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>152703</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="n">
-        <v>122</v>
-      </c>
-      <c r="N22" s="2" t="n">
-        <v>84045</v>
+          <t>145950</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>156892</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>93,9%</t>
+        </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>347</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>261740</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>253149</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>268493</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>92,8%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>89,75%</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>95,2%</t>
         </is>
       </c>
     </row>
@@ -2040,146 +2878,1029 @@
       <c r="A23" s="1" t="n"/>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="n">
-        <v>871</v>
-      </c>
-      <c r="D23" s="2" t="n">
-        <v>619900</v>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>119428</t>
+        </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>119428</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>119428</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="n">
-        <v>894</v>
-      </c>
-      <c r="I23" s="2" t="n">
-        <v>701894</v>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>198</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>162617</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="n">
-        <v>1765</v>
-      </c>
-      <c r="N23" s="2" t="n">
-        <v>1321794</v>
+          <t>162617</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>162617</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>378</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>282045</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>282045</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>282045</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n"/>
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="n">
-        <v>929</v>
-      </c>
-      <c r="D24" s="2" t="n">
-        <v>657337</v>
+          <t>Sí, por algún síntoma</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>2928</t>
+        </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>1011</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>6849</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="n">
-        <v>958</v>
-      </c>
-      <c r="I24" s="2" t="n">
-        <v>748502</v>
+          <t>4,25%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>9,94%</t>
+        </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>3421</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="n">
-        <v>1887</v>
-      </c>
-      <c r="N24" s="2" t="n">
-        <v>1405839</v>
+          <t>847</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>8065</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>4,75%</t>
+        </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>6349</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>2934</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>11631</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>4,51%</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>2,08%</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>8,25%</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="1" t="n"/>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Sí, por algún dolor</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>815</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>4640</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>1,18%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>6,73%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>815</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>4454</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>0,58%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>3,16%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>65151</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>61286</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>67629</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>94,57%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>88,96%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>98,16%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>68582</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>63938</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>71156</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>95,25%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>88,8%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>98,82%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>133733</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>128088</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>137490</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>94,91%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>90,91%</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>97,58%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>68895</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>68895</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>68895</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>72003</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>72003</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>72003</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>140898</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>140898</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t>140898</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Sí, por algún síntoma</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>26858</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>19435</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>35364</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>4,09%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>2,96%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>5,38%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>34744</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>25591</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>46747</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>4,64%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>3,42%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>6,25%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>61602</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>48675</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>75887</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>4,38%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>3,46%</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>5,4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Sí, por algún dolor</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>10579</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>6129</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>17014</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>2,59%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>11864</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>7103</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>19688</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>1,59%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>0,95%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>2,63%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>22443</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>15195</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>31415</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>1,6%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>2,23%</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>871</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>619900</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>609046</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>629110</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>94,3%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>92,65%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>95,71%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>894</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>701894</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>687738</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>712691</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>93,77%</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>91,88%</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>95,22%</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>1765</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>1321794</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>1306101</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>1337391</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>94,02%</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>92,91%</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>95,13%</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n"/>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>657337</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>657337</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>657337</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>958</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>748502</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>748502</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>748502</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>1887</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>1405839</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>1405839</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>1405839</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -2187,17 +3908,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="A4:A6"/>
-    <mergeCell ref="A16:A18"/>
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="C1:G1"/>
-    <mergeCell ref="A19:A21"/>
-    <mergeCell ref="H1:L1"/>
+    <mergeCell ref="J1:P1"/>
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A28:A31"/>
+    <mergeCell ref="A20:A23"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A22:A24"/>
-    <mergeCell ref="M1:Q1"/>
-    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="Q1:W1"/>
+    <mergeCell ref="C1:I1"/>
+    <mergeCell ref="A24:A27"/>
+    <mergeCell ref="A16:A19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/trans_orig/IP13_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP13_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si se han tenido que quedar más de la mitad del día en la cama por dolor o síntomas 2023 en 2023 (tasa de respuesta: 99,95%)</t>
+          <t>Menores según si en las últimas 2 semanas se han tenido que quedar más de la mitad del día en la cama por dolor o síntomas 2023 en 2023 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1070</t>
+          <t>1013</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6700</t>
+          <t>6856</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>870</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7818</t>
+          <t>8405</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2780</t>
+          <t>2764</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11587</t>
+          <t>11006</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1323</t>
+          <t>1349</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8022</t>
+          <t>8748</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6129</t>
+          <t>6144</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2283</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11530</t>
+          <t>11818</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,91%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>93172</t>
+          <t>92362</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>101241</t>
+          <t>101210</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>88,42%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>125432</t>
+          <t>125541</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>134255</t>
+          <t>134400</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>222118</t>
+          <t>222274</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>234503</t>
+          <t>234109</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,28%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1511</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8438</t>
+          <t>8998</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3247</t>
+          <t>3063</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11938</t>
+          <t>11063</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6382</t>
+          <t>6181</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>16584</t>
+          <t>17110</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,99%</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3809</t>
+          <t>3558</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7031</t>
+          <t>6741</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>968</t>
+          <t>680</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>8054</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>84932</t>
+          <t>84628</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>92532</t>
+          <t>92616</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>80612</t>
+          <t>80927</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>90482</t>
+          <t>90529</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>84,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>168994</t>
+          <t>169391</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>181393</t>
+          <t>181925</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,62%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>395</t>
+          <t>391</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4947</t>
+          <t>4708</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>859</t>
+          <t>814</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7336</t>
+          <t>6403</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>2093</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9385</t>
+          <t>9811</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,48%</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3970</t>
+          <t>3766</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2931</t>
+          <t>3215</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>389</t>
+          <t>400</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4643</t>
+          <t>4322</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>45277</t>
+          <t>45822</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>50816</t>
+          <t>50784</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>88,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>55635</t>
+          <t>56392</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>62553</t>
+          <t>62683</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>104494</t>
+          <t>104289</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>112453</t>
+          <t>112538</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,26%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2748</t>
+          <t>2643</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11271</t>
+          <t>11829</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6489</t>
+          <t>6787</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18479</t>
+          <t>18963</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11042</t>
+          <t>11039</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26218</t>
+          <t>25932</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>568</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7525</t>
+          <t>7157</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2226,12 +2226,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1716</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9366</t>
+          <t>10366</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3439</t>
+          <t>3065</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>13305</t>
+          <t>12839</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>202395</t>
+          <t>202444</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>213329</t>
+          <t>213574</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>194944</t>
+          <t>193975</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>208535</t>
+          <t>208633</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>401347</t>
+          <t>401811</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>419328</t>
+          <t>419707</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,2%</t>
         </is>
       </c>
     </row>
@@ -2554,12 +2554,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4910</t>
+          <t>4965</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>14283</t>
+          <t>14736</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3750</t>
+          <t>3389</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13902</t>
+          <t>13321</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>9924</t>
+          <t>10654</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>23818</t>
+          <t>24008</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,12 +2639,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,51%</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4265</t>
+          <t>4764</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>753</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7066</t>
+          <t>6591</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2742,7 +2742,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>9037</t>
+          <t>9243</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>103695</t>
+          <t>103150</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>113497</t>
+          <t>113182</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>145950</t>
+          <t>146601</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>156892</t>
+          <t>157023</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2830,12 +2830,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2850,12 +2850,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>253149</t>
+          <t>252786</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>268493</t>
+          <t>267812</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>94,95%</t>
         </is>
       </c>
     </row>
@@ -3010,12 +3010,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1011</t>
+          <t>957</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6849</t>
+          <t>6424</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3025,12 +3025,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3045,12 +3045,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>847</t>
+          <t>882</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8065</t>
+          <t>8191</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3080,12 +3080,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2934</t>
+          <t>2957</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>11631</t>
+          <t>11216</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3095,12 +3095,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>7,96%</t>
         </is>
       </c>
     </row>
@@ -3128,7 +3128,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4640</t>
+          <t>4077</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3198,7 +3198,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4454</t>
+          <t>4815</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -3236,12 +3236,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>61286</t>
+          <t>61064</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>67629</t>
+          <t>67568</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3271,12 +3271,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>63938</t>
+          <t>63812</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>71156</t>
+          <t>71121</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3286,12 +3286,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3306,12 +3306,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>128088</t>
+          <t>128176</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>137490</t>
+          <t>137290</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,44%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>19435</t>
+          <t>19825</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>35364</t>
+          <t>36416</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>25591</t>
+          <t>25220</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>46747</t>
+          <t>45072</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>48675</t>
+          <t>47974</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>75887</t>
+          <t>74879</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,33%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>6129</t>
+          <t>5763</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>17014</t>
+          <t>16653</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>7103</t>
+          <t>6880</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>19688</t>
+          <t>19047</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>15195</t>
+          <t>15864</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>31415</t>
+          <t>31699</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>609046</t>
+          <t>609653</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>629110</t>
+          <t>629172</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>687738</t>
+          <t>689516</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>712691</t>
+          <t>713063</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1306101</t>
+          <t>1305670</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1337391</t>
+          <t>1337325</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">

--- a/data/trans_orig/IP13_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP13_2023-Clase-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3140</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>871</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8035</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2,57%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>6,58%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2866</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1013</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6856</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,74%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>6,56%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3331</t>
+          <t>2957</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>1193</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8405</t>
+          <t>6833</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>6096</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2764</t>
+          <t>2665</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11006</t>
+          <t>11532</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1826</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>6419</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1,5%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>5,26%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>3773</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1349</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>8748</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>3,61%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1,29%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>8,37%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1707</t>
+          <t>3857</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1375</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6144</t>
+          <t>9000</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>5479</t>
+          <t>5683</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2271</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11818</t>
+          <t>11223</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,99%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>117072</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>112065</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>120276</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>95,93%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>91,83%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>98,56%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>147</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>97823</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>92362</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>101210</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>93,65%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>88,42%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>96,89%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>131146</t>
+          <t>96113</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>125541</t>
+          <t>90470</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>134400</t>
+          <t>99181</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>87,9%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>228969</t>
+          <t>213186</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>222274</t>
+          <t>206228</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>234109</t>
+          <t>218210</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,0%</t>
         </is>
       </c>
     </row>
@@ -1059,57 +1059,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>122038</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>122038</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>122038</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>157</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>104462</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>104462</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>104462</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>136184</t>
+          <t>102927</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>136184</t>
+          <t>102927</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>136184</t>
+          <t>102927</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>240646</t>
+          <t>224965</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>240646</t>
+          <t>224965</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>240646</t>
+          <t>224965</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>6363</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3166</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>11562</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>6,96%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>3,46%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>12,65%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>4364</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1513</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>8998</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>4,61%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1,6%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>9,5%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>6356</t>
+          <t>4259</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3063</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11063</t>
+          <t>8979</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>10719</t>
+          <t>10622</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6181</t>
+          <t>6388</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>17110</t>
+          <t>17789</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,47%</t>
         </is>
       </c>
     </row>
@@ -1289,72 +1289,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>2422</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>467</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>6832</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>2,65%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>7,48%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>651</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>3558</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>3340</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>0,67%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>3,76%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>2529</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>548</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>6741</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>2,65%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>3181</t>
+          <t>3065</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>921</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8054</t>
+          <t>7911</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,21%</t>
         </is>
       </c>
     </row>
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>82613</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>76594</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>86512</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>90,39%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>83,8%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>94,65%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>134</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>89666</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>84628</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>92616</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>94,7%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>89,38%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>97,82%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>86688</t>
+          <t>91645</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>80927</t>
+          <t>87065</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>90529</t>
+          <t>94517</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>176354</t>
+          <t>174257</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>169391</t>
+          <t>165794</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>181925</t>
+          <t>178950</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,21%</t>
         </is>
       </c>
     </row>
@@ -1515,57 +1515,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>91398</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>91398</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>91398</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>141</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>94681</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>94681</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>94681</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>95573</t>
+          <t>96546</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>95573</t>
+          <t>96546</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>95573</t>
+          <t>96546</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>190254</t>
+          <t>187944</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>190254</t>
+          <t>187944</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>190254</t>
+          <t>187944</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1632,72 +1632,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2996</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>889</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>7528</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>5,26%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>13,22%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>1687</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>391</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>4708</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>3,25%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>9,08%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2904</t>
+          <t>1596</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>814</t>
+          <t>355</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6403</t>
+          <t>4598</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>4591</t>
+          <t>4592</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2093</t>
+          <t>1793</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9811</t>
+          <t>9381</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,5%</t>
         </is>
       </c>
     </row>
@@ -1745,72 +1745,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2432</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,27%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>1060</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>988</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3766</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>2,04%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3681</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>1,85%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>7,26%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>549</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3215</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1609</t>
+          <t>1443</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>336</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4322</t>
+          <t>4207</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -1858,72 +1858,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>53490</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>48933</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>55738</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>93,94%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>85,94%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>97,89%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>49114</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>45822</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>50784</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>94,7%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>88,35%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>97,92%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>60400</t>
+          <t>50898</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>56392</t>
+          <t>47340</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>62683</t>
+          <t>52533</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>109514</t>
+          <t>104388</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>104289</t>
+          <t>99465</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>112538</t>
+          <t>107459</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,32%</t>
         </is>
       </c>
     </row>
@@ -1971,57 +1971,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>56941</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>56941</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>56941</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>51861</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>51861</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>51861</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>63853</t>
+          <t>53482</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>63853</t>
+          <t>53482</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>63853</t>
+          <t>53482</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>115714</t>
+          <t>110423</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>115714</t>
+          <t>110423</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>115714</t>
+          <t>110423</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2088,72 +2088,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>10004</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>5478</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>16232</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>4,95%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2,71%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>8,04%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>6148</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>2643</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>11829</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2,82%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,21%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>5,43%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>11528</t>
+          <t>6022</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6787</t>
+          <t>2833</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18963</t>
+          <t>11033</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>17676</t>
+          <t>16026</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11039</t>
+          <t>10381</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25932</t>
+          <t>23555</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,19%</t>
         </is>
       </c>
     </row>
@@ -2201,72 +2201,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>4025</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1435</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>9945</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1,99%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>4,92%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>2753</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>568</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>7157</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>1,26%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>3,28%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4369</t>
+          <t>2864</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>953</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10366</t>
+          <t>7384</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>7122</t>
+          <t>6889</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3065</t>
+          <t>3291</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>12839</t>
+          <t>12955</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -2314,72 +2314,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>187915</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>180348</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>192971</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>93,05%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>89,31%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>95,56%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>264</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>209109</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>202444</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>213574</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>95,92%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>92,86%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>97,97%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>202375</t>
+          <t>169927</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>193975</t>
+          <t>165078</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>208633</t>
+          <t>174132</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>411484</t>
+          <t>357842</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>401811</t>
+          <t>349132</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>419707</t>
+          <t>364981</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>95,86%</t>
         </is>
       </c>
     </row>
@@ -2427,57 +2427,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>201944</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>201944</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>201944</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>277</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>218010</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>218010</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>218010</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>285</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>218272</t>
+          <t>178813</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>218272</t>
+          <t>178813</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>218272</t>
+          <t>178813</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>436282</t>
+          <t>380758</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>436282</t>
+          <t>380758</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>436282</t>
+          <t>380758</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2544,72 +2544,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>6694</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>3707</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>12231</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>4,52%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>2,5%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>8,25%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>8865</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>4965</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>14736</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>7,42%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>4,16%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>12,34%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3389</t>
+          <t>4703</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13321</t>
+          <t>13535</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>16069</t>
+          <t>14993</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>10654</t>
+          <t>9787</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>24008</t>
+          <t>22445</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,41%</t>
         </is>
       </c>
     </row>
@@ -2657,72 +2657,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>2670</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>728</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>7338</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>4,95%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>1527</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>388</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>4764</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>3,99%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2710</t>
+          <t>1497</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>753</t>
+          <t>339</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6591</t>
+          <t>4512</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,32 +2732,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>4236</t>
+          <t>4166</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1827</t>
+          <t>1716</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>9243</t>
+          <t>8897</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -2770,72 +2770,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>138879</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>132555</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>142820</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>93,68%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>89,42%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>96,34%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>163</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>109037</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>103150</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>113182</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>91,3%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>86,37%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>94,77%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>152703</t>
+          <t>108936</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>146601</t>
+          <t>103486</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>157023</t>
+          <t>113066</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,32 +2845,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>261740</t>
+          <t>247815</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>252786</t>
+          <t>239831</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>267812</t>
+          <t>253866</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>95,09%</t>
         </is>
       </c>
     </row>
@@ -2883,57 +2883,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>148243</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>148243</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>148243</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>180</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>119428</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>119428</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>119428</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>162617</t>
+          <t>118731</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>162617</t>
+          <t>118731</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>162617</t>
+          <t>118731</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>282045</t>
+          <t>266974</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>282045</t>
+          <t>266974</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>282045</t>
+          <t>266974</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3000,72 +3000,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>3488</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>909</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>8289</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>5,11%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>1,33%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>12,14%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>2928</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>957</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>6424</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>4,25%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>9,32%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3421</t>
+          <t>3106</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>882</t>
+          <t>1011</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8191</t>
+          <t>7593</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,32 +3075,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6349</t>
+          <t>6594</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2957</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>11216</t>
+          <t>11870</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,56%</t>
         </is>
       </c>
     </row>
@@ -3113,107 +3113,107 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>815</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>690</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>4077</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>3681</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>5,92%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>5,23%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>690</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>4240</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>815</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>4815</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -3226,72 +3226,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>64799</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>59998</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>67378</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>94,89%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>87,86%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>98,67%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>65151</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>61064</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>67568</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>94,57%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>88,63%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>98,07%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>68582</t>
+          <t>66560</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>63812</t>
+          <t>61905</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>71121</t>
+          <t>68904</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,32 +3301,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>133733</t>
+          <t>131360</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>128176</t>
+          <t>125496</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>137290</t>
+          <t>134988</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,36%</t>
         </is>
       </c>
     </row>
@@ -3339,57 +3339,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>68287</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>68287</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>68287</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>72003</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>72003</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>72003</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3414,17 +3414,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>140898</t>
+          <t>138644</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>140898</t>
+          <t>138644</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>140898</t>
+          <t>138644</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3456,72 +3456,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>32685</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>23399</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>43240</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>4,74%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>3,4%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>6,28%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>26858</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>19825</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>36416</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>4,09%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>3,02%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>5,54%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>34744</t>
+          <t>26239</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>25220</t>
+          <t>19506</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>45072</t>
+          <t>35958</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,32 +3531,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>61602</t>
+          <t>58924</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>47974</t>
+          <t>48267</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>74879</t>
+          <t>74030</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,65%</t>
         </is>
       </c>
     </row>
@@ -3574,32 +3574,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>10579</t>
+          <t>11398</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5763</t>
+          <t>6207</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>16653</t>
+          <t>18847</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,32 +3609,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>11864</t>
+          <t>10538</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>6880</t>
+          <t>6334</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>19047</t>
+          <t>17908</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,32 +3644,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>22443</t>
+          <t>21936</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>15864</t>
+          <t>14941</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>31699</t>
+          <t>30440</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -3682,72 +3682,72 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>894</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>644768</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>632439</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>656094</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>93,6%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>91,81%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>95,24%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>871</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>619900</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>609653</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>629172</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>94,3%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>92,75%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>95,72%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>894</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>701894</t>
+          <t>584080</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>689516</t>
+          <t>573425</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>713063</t>
+          <t>592285</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,32 +3757,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1321794</t>
+          <t>1228847</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1305670</t>
+          <t>1212970</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1337325</t>
+          <t>1241292</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>94,78%</t>
         </is>
       </c>
     </row>
@@ -3795,57 +3795,57 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>958</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>688851</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>688851</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>688851</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>929</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>657337</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>657337</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>657337</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>958</t>
-        </is>
-      </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>748502</t>
+          <t>620857</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>748502</t>
+          <t>620857</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>748502</t>
+          <t>620857</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3870,17 +3870,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>1405839</t>
+          <t>1309707</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1405839</t>
+          <t>1309707</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1405839</t>
+          <t>1309707</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
